--- a/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
@@ -647,25 +647,25 @@
         <v>40</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6" s="1">
+        <v>80</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6" s="1">
         <v>10</v>
-      </c>
-      <c r="G6" s="1">
-        <v>75</v>
-      </c>
-      <c r="H6" s="1">
-        <v>25</v>
-      </c>
-      <c r="I6" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6" s="1">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1287,25 +1287,25 @@
         <v>40</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6" s="1">
+        <v>80</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6" s="1">
         <v>10</v>
-      </c>
-      <c r="G6" s="1">
-        <v>75</v>
-      </c>
-      <c r="H6" s="1">
-        <v>25</v>
-      </c>
-      <c r="I6" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6" s="1">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:11">

--- a/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
@@ -577,25 +577,25 @@
         <v>37</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -612,25 +612,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -659,13 +659,13 @@
         <v>20</v>
       </c>
       <c r="I6" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -839,22 +839,25 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F2">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>12.82</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.6</v>
       </c>
       <c r="J2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -903,22 +906,25 @@
         <v>37</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>91.89</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>8.109999999999999</v>
+      </c>
+      <c r="I4" s="2">
+        <v>9.4</v>
       </c>
       <c r="J4">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -935,22 +941,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>81.08</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>18.92</v>
+      </c>
+      <c r="I5" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J5">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -967,22 +976,25 @@
         <v>40</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6" s="1">
+        <v>60</v>
+      </c>
+      <c r="H6" s="1">
         <v>40</v>
       </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1">
-        <v>100</v>
+      <c r="I6" s="2">
+        <v>7.8</v>
       </c>
       <c r="J6">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -999,22 +1011,25 @@
         <v>39</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>94.87</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>5.13</v>
+      </c>
+      <c r="I7" s="2">
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1031,22 +1046,25 @@
         <v>32</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>15.63</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J8">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1147,19 +1165,19 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>84.62</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>15.38</v>
+        <v>12.82</v>
       </c>
       <c r="I2" s="2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1217,25 +1235,25 @@
         <v>37</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
         <v>9.4</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1252,25 +1270,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1299,13 +1317,13 @@
         <v>20</v>
       </c>
       <c r="I6" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1322,19 +1340,19 @@
         <v>39</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>97.44</v>
+        <v>94.87</v>
       </c>
       <c r="H7" s="1">
-        <v>2.56</v>
+        <v>5.13</v>
       </c>
       <c r="I7" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1357,19 +1375,19 @@
         <v>32</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>90.63</v>
+        <v>84.38</v>
       </c>
       <c r="H8" s="1">
-        <v>9.380000000000001</v>
+        <v>15.63</v>
       </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J8">
         <v>0</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
@@ -906,25 +906,25 @@
         <v>37</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>91.89</v>
+        <v>94.59</v>
       </c>
       <c r="H4" s="1">
-        <v>8.109999999999999</v>
+        <v>5.41</v>
       </c>
       <c r="I4" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" s="1">
-        <v>8.109999999999999</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -941,25 +941,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>81.08</v>
+        <v>97.3</v>
       </c>
       <c r="H5" s="1">
-        <v>18.92</v>
+        <v>2.7</v>
       </c>
       <c r="I5" s="2">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>18.92</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -976,25 +976,25 @@
         <v>40</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H6" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I6" s="2">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>27.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1247,7 +1247,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1317,7 +1317,7 @@
         <v>20</v>
       </c>
       <c r="I6" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J6">
         <v>0</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
@@ -874,22 +874,25 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I3" s="2">
+        <v>7.5</v>
       </c>
       <c r="J3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1212,7 +1215,7 @@
         <v>9.380000000000001</v>
       </c>
       <c r="I3" s="2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J3">
         <v>0</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
@@ -909,25 +909,25 @@
         <v>37</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>5.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -944,25 +944,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">

--- a/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
@@ -1084,22 +1084,25 @@
         <v>40</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>75</v>
+      </c>
+      <c r="I9" s="2">
+        <v>9.6</v>
       </c>
       <c r="J9">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1425,7 +1428,7 @@
         <v>75</v>
       </c>
       <c r="I9" s="2">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J9">
         <v>30</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
@@ -752,25 +752,25 @@
         <v>40</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1">
-        <v>25</v>
+        <v>77.5</v>
       </c>
       <c r="H9" s="1">
-        <v>75</v>
+        <v>22.5</v>
       </c>
       <c r="I9" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1084,25 +1084,25 @@
         <v>40</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1">
-        <v>25</v>
+        <v>77.5</v>
       </c>
       <c r="H9" s="1">
-        <v>75</v>
+        <v>22.5</v>
       </c>
       <c r="I9" s="2">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1416,25 +1416,25 @@
         <v>40</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1">
-        <v>25</v>
+        <v>77.5</v>
       </c>
       <c r="H9" s="1">
-        <v>75</v>
+        <v>22.5</v>
       </c>
       <c r="I9" s="2">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
@@ -644,28 +644,28 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6">
         <v>32</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="H6" s="1">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="I6" s="2">
         <v>7.6</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -749,28 +749,28 @@
         <v>20</v>
       </c>
       <c r="D9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E9">
         <v>31</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>77.5</v>
+        <v>73.81</v>
       </c>
       <c r="H9" s="1">
-        <v>22.5</v>
+        <v>26.19</v>
       </c>
       <c r="I9" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
   </sheetData>
@@ -976,28 +976,28 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6">
         <v>32</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="H6" s="1">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="I6" s="2">
         <v>7.1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1081,28 +1081,28 @@
         <v>20</v>
       </c>
       <c r="D9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E9">
         <v>31</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>77.5</v>
+        <v>73.81</v>
       </c>
       <c r="H9" s="1">
-        <v>22.5</v>
+        <v>26.19</v>
       </c>
       <c r="I9" s="2">
         <v>8.5</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
   </sheetData>
@@ -1308,28 +1308,28 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6">
         <v>32</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="H6" s="1">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="I6" s="2">
         <v>7.5</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1381,19 +1381,19 @@
         <v>32</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="H8" s="1">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
       <c r="I8" s="2">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1413,28 +1413,28 @@
         <v>20</v>
       </c>
       <c r="D9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E9">
         <v>31</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>77.5</v>
+        <v>73.81</v>
       </c>
       <c r="H9" s="1">
-        <v>22.5</v>
+        <v>26.19</v>
       </c>
       <c r="I9" s="2">
         <v>8.4</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
@@ -1416,19 +1416,19 @@
         <v>42</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" s="1">
-        <v>73.81</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>26.19</v>
+        <v>28.57</v>
       </c>
       <c r="I9" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>2</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
@@ -1171,19 +1171,19 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>87.18000000000001</v>
+        <v>97.44</v>
       </c>
       <c r="H2" s="1">
-        <v>12.82</v>
+        <v>2.56</v>
       </c>
       <c r="I2" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1206,19 +1206,19 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>90.63</v>
+        <v>87.5</v>
       </c>
       <c r="H3" s="1">
-        <v>9.380000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="I3" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1253,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J5">
         <v>0</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
@@ -1323,7 +1323,7 @@
         <v>23.81</v>
       </c>
       <c r="I6" s="2">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="J6">
         <v>2</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20221.xlsx
@@ -647,25 +647,25 @@
         <v>42</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>76.19</v>
+        <v>80.95</v>
       </c>
       <c r="H6" s="1">
-        <v>23.81</v>
+        <v>19.05</v>
       </c>
       <c r="I6" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -752,25 +752,25 @@
         <v>42</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>73.81</v>
+        <v>76.19</v>
       </c>
       <c r="H9" s="1">
-        <v>26.19</v>
+        <v>23.81</v>
       </c>
       <c r="I9" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -979,25 +979,25 @@
         <v>42</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>76.19</v>
+        <v>80.95</v>
       </c>
       <c r="H6" s="1">
-        <v>23.81</v>
+        <v>19.05</v>
       </c>
       <c r="I6" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1084,25 +1084,25 @@
         <v>42</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>73.81</v>
+        <v>76.19</v>
       </c>
       <c r="H9" s="1">
-        <v>26.19</v>
+        <v>23.81</v>
       </c>
       <c r="I9" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1311,25 +1311,25 @@
         <v>42</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>76.19</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>23.81</v>
+        <v>14.29</v>
       </c>
       <c r="I6" s="2">
         <v>7.3</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1416,25 +1416,25 @@
         <v>42</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>71.43000000000001</v>
+        <v>73.81</v>
       </c>
       <c r="H9" s="1">
-        <v>28.57</v>
+        <v>26.19</v>
       </c>
       <c r="I9" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
